--- a/Data_Fig_S25_D,E.xlsx
+++ b/Data_Fig_S25_D,E.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="per_trial" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -599,4 +600,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nozzle</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>tau/T</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Trial</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Speed_BL_s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Acceleration_BL_s2</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Power_W</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Rigid</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1881528544599223</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.02035368464648471</v>
+      </c>
+      <c r="F2" t="n">
+        <v>9.528651956457781</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rigid</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1827602157788424</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02161092931527957</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.354848237769595</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Rigid</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1818328901120906</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.02123386434852517</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.465655577689244</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rigid</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1893117305504696</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02304727492929986</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.330492909535453</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Rigid</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1925075919285366</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.0217690091627594</v>
+      </c>
+      <c r="F6" t="n">
+        <v>9.419343254292722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>05mm</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2087992811455257</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02330050360746707</v>
+      </c>
+      <c r="F7" t="n">
+        <v>8.885</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>05mm</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2088169130263511</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02275426436190664</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9.051676597789525</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>05mm</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2104747533561214</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.02518459125058986</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9.089374127159134</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>05mm</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.21803460368603</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.02404906133942717</v>
+      </c>
+      <c r="F10" t="n">
+        <v>9.118365340406719</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>05mm</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2110114393519891</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.02559163698980821</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9.144919189719015</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.243906567945766</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.02782911434658372</v>
+      </c>
+      <c r="F12" t="n">
+        <v>9.086630872483221</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.258956030635159</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02857521556940954</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.170028565245619</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.267227472121333</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.02866409398449138</v>
+      </c>
+      <c r="F14" t="n">
+        <v>9.21375415730337</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2478581480908253</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.0304125183677475</v>
+      </c>
+      <c r="F15" t="n">
+        <v>9.034376149068322</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10mm</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.2553852144046939</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.02965253287698398</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.045765041165295</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15mm</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2602644191028315</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.02761511582849091</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9.079221069433361</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15mm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2715731234043761</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.02709226021412158</v>
+      </c>
+      <c r="F18" t="n">
+        <v>9.168940322580646</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15mm</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.2664925904949635</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.02842168754116951</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9.271010253082414</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15mm</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.2650106339857502</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.03067053532923089</v>
+      </c>
+      <c r="F20" t="n">
+        <v>9.278098924731182</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15mm</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.2692892784692969</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02877512660873761</v>
+      </c>
+      <c r="F21" t="n">
+        <v>9.247860980207351</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.2393476417697684</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.02648392504703388</v>
+      </c>
+      <c r="F22" t="n">
+        <v>9.283883130291143</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2496258339264507</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.02742439424044475</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.227944459872258</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.2268074051125192</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.03013365088479194</v>
+      </c>
+      <c r="F24" t="n">
+        <v>9.294245023466582</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2426046600717124</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.02818578098232405</v>
+      </c>
+      <c r="F25" t="n">
+        <v>9.155481262327415</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20mm</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.2355325298925734</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.02414106353186855</v>
+      </c>
+      <c r="F26" t="n">
+        <v>9.220366533864542</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25mm</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.228253272207214</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.02713686853660202</v>
+      </c>
+      <c r="F27" t="n">
+        <v>9.278726653903425</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25mm</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.2184039763164058</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.02802435945574835</v>
+      </c>
+      <c r="F28" t="n">
+        <v>9.213809452643378</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>25mm</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.2032433965131498</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0276069545488661</v>
+      </c>
+      <c r="F29" t="n">
+        <v>9.263092086098075</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>25mm</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.2276881421279992</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.02726326316714803</v>
+      </c>
+      <c r="F30" t="n">
+        <v>9.233928236268286</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>25mm</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="C31" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.218960983715841</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.02750293442825055</v>
+      </c>
+      <c r="F31" t="n">
+        <v>9.196923224568138</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>30mm</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.2221348963197799</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.02648866302160252</v>
+      </c>
+      <c r="F32" t="n">
+        <v>9.229329527763362</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>30mm</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.2113972160975312</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0247006600688631</v>
+      </c>
+      <c r="F33" t="n">
+        <v>9.247042956656347</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>30mm</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.2264871757809317</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.02650636552708833</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.257404938863582</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>30mm</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.2055536534044495</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.02743836482788214</v>
+      </c>
+      <c r="F35" t="n">
+        <v>9.212248344370861</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>30mm</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2220141837010358</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.02523788664038938</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9.246336907314747</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>